--- a/Machine_Learning/data_all.xlsx
+++ b/Machine_Learning/data_all.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\博-实验记录\实验数据\苯乙酮体系\写文章\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vscode\111\ML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314A1651-A059-44A4-8188-430FFDE1891D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91F5642-DFBA-4C6E-B89A-16867887FF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="450" yWindow="0" windowWidth="28350" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="batch1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t>ton</t>
   </si>
@@ -79,86 +79,6 @@
     <t>20-G,F,Y,Y,K,A,T,N,H,F</t>
   </si>
   <si>
-    <t>21-D,E,T,W,K,I,Q,D,C,M-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>22-A,P,M,F,K,D,V,H,W,P-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>23-W,T,G,S,K,D,T,C,Q,N-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>24-M,V,M,C,K,R,P,F,P,P-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>25-L,V,N,I,K,G,H,F,P,P-0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>26-F,P,N,C,K,S,M,C,C,V-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>27-P,Q,G,G,K,D,D,H,Q,N-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>28-T,C,V,D,K,F,S,N,Y,D-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>29-P,Q,G,I,K,D,D,C,Q,L-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>30-P,V,M,C,K,Y,P,F,A,P-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>31-G,V,M,C,K,G,P,F,L,P-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>32-T,R,V,D,K,F,S,N,Y,D-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>33-N,Q,F,L,K,H,D,C,D,I-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>34-S,V,M,C,K,G,P,W,P,P-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>35-P,P,H,C,K,S,Y,I,E,S-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>36-A,Q,M,L,K,H,T,C,M,G-3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>37-D,E,T,I,K,I,W,Y,A,M-0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>38-M,T,G,A,K,D,D,C,Q,T-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>39-V,D,V,D,K,F,S,F,L,D-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>40-I,F,Y,I,K,V,A,N,M,D-0</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>41-N,L,N,E,K,V,V,Q,E,M</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -239,428 +159,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>61-F,P,N,W,K,S,M,D,C,V-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>62-A,V,H,C,K,S,V,I,W,S-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>63-W,E,T,S,K,I,T,Y,A,M-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>64-S,V,M,C,K,R,P,W,P,P-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>65-L,V,N,I,K,G,H,W,P,P-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>66-F,V,M,C,K,S,P,F,P,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>67-W,Q,G,S,K,D,T,H,Q,N-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>68-P,C,N,C,K,H,M,C,C,V-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>69-W,Q,G,I,K,D,T,C,Q,L-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>70-P,V,M,C,K,Y,P,W,A,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>exp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>80-D,E,S,T,K,I,Q,Y,V,M-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>81-F,P,N,W,K,S,W,D,C,V-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>82-A,P,N,C,K,H,V,F,W,V-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>83-W,E,T,S,K,I,T,Y,A,T-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>84-G,V,M,C,K,R,P,W,L,P-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>85-L,V,N,I,K,G,H,W,L,P-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>86-F,V,M,C,K,S,T,F,M,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>87-M,Q,T,A,K,I,W,H,A,T-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>88-V,C,N,C,K,H,M,F,L,V-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>89-M,Q,T,I,K,I,W,Y,A,L-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90-V,R,N,C,K,H,M,F,L,V-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>91-D,E,S,T,K,I,Q,Y,V,I-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>92-S,V,M,C,K,G,P,W,L,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>93-W,P,G,I,K,D,Y,C,Q,N-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>94-A,E,M,T,K,I,T,Y,M,M-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>95-M,P,M,A,K,G,Y,F,L,T-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>96-G,P,S,T,K,G,Y,F,V,P-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>97-G,V,F,C,K,W,P,W,L,V-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>98-P,V,M,C,K,G,T,F,M,Q-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>99-R,V,I,C,K,G,T,F,M,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100-M,V,M,L,K,G,P,Y,P,I-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>71-G,V,M,C,K,G,P,W,L,P-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>72-P,R,N,C,K,H,M,C,C,V-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>73-M,V,M,C,K,G,P,F,P,I-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>74-G,P,M,C,K,G,Y,F,L,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>75-A,V,M,C,K,G,T,F,M,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>76-F,P,N,C,K,S,W,C,C,V-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>77-M,E,T,A,K,I,W,Y,A,T-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>78-V,P,N,C,K,H,M,F,L,V-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>79-W,T,G,I,K,D,T,C,Q,N-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1-I,F,Y,G,K,V,A,N,M,D</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>第一轮随机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第六轮迭代</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2-L,V,Q,Y,K,N,C,F,P,E</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>101-G,V,M,S,K,G,T,F,L,Q-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>102-P,R,M,I,K,G,T,F,M,L-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>103-F,Q,S,T,K,S,Y,H,V,I-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>104-S,V,M,S,K,G,T,W,M,Q-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>105-A,P,I,C,K,S,Y,C,W,V-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>106-A,Q,M,T,K,S,T,H,M,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>107-M,P,I,A,K,S,V,C,W,T-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>108-V,V,M,C,K,Y,P,F,L,I-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>109-S,P,M,I,K,G,Y,D,C,P-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>110-S,P,S,T,K,G,Y,D,V,P-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第八轮迭代</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第九轮迭代</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>121-M,V,M,W,K,G,I,F,C,I-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>122-A,P,M,V,K,W,D,F,P,P-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>123-F,V,C,C,K,I,S,R,P,G-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>124-F,R,N,C,K,S,M,I,C,V-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>125-F,V,M,T,K,L,P,N,I,P-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>126-M,V,M,C,K,F,P,F,P,P-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>127-M,V,M,C,K,G,Q,H,P,I-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>128-Q,V,Q,W,K,S,P,F,P,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>129-S,V,M,C,K,Q,P,I,P,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>130-T,L,M,P,K,G,Y,F,C,I-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>111-G,V,M,W,K,G,T,D,C,Q-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>112-A,Q,M,T,K,S,V,H,W,P-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>113-W,Q,S,S,K,S,T,H,V,I-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>114-P,R,M,I,K,R,T,F,M,L-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>115-L,Q,N,I,K,S,H,H,M,P-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>116-F,P,I,A,K,S,V,C,W,T-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>117-S,Q,M,I,K,G,Y,H,C,P-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>118-P,C,M,I,K,G,T,F,M,L-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>119-S,Q,M,I,K,G,Y,D,C,L-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>120-P,V,M,S,K,Y,T,F,A,Q-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第十轮迭代</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>131-Q,V,Q,W,K,S,I,F,C,P-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>132-Q,V,C,W,K,I,S,R,P,G-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>133-S,R,M,C,K,Q,P,I,P,P-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>134-M,V,M,T,K,L,P,N,I,P-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>135-F,V,M,T,K,F,P,N,I,P-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>136-S,V,M,C,K,Q,Q,H,P,P-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>137-Q,P,Q,W,K,W,D,F,P,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>138-M,V,M,C,K,Q,P,I,P,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>139-T,L,M,P,K,Q,Y,I,C,P-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>140-A,P,M,V,K,W,D,Y,P,C-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>141-F,V,M,W,K,F,I,N,C,P-2</t>
-  </si>
-  <si>
-    <t>142-A,P,M,V,K,W,D,N,I,P-1</t>
-  </si>
-  <si>
-    <t>143-S,R,C,C,K,I,S,R,P,G-1</t>
-  </si>
-  <si>
-    <t>144-A,R,M,V,K,W,D,I,P,C-1</t>
-  </si>
-  <si>
-    <t>145-T,L,M,T,K,L,Y,N,I,P-2</t>
-  </si>
-  <si>
-    <t>146-S,V,M,C,K,F,Q,H,P,P-0</t>
-  </si>
-  <si>
-    <t>147-Q,P,Q,W,K,W,Q,H,P,P-0</t>
-  </si>
-  <si>
-    <t>148-Q,V,Q,W,K,L,P,N,I,P-3</t>
-  </si>
-  <si>
-    <t>149-S,V,M,C,K,Q,Q,I,P,P-3</t>
-  </si>
-  <si>
-    <t>150-T,L,Q,P,K,W,Y,F,C,P-0</t>
-  </si>
-  <si>
-    <t>151-A,R,M,C,K,W,L,I,M,C-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>152-F,L,Q,R,K,W,C,V,C,C-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>153-F,R,M,W,K,V,G,N,C,P-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>154-Q,S,V,M,K,W,Q,H,P,G-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>155-T,L,M,T,K,L,Y,P,R,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>156-T,L,M,C,K,R,Q,I,P,G-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>157-T,L,C,T,K,L,Y,N,I,P-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>158-C,G,C,C,K,G,S,R,G,S-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>159-Q,F,Q,W,K,W,Q,H,P,P-3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>160-F,R,S,W,K,C,L,N,L,P-0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>161-T,C,M,M,K,T,T,C,M,T</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -693,10 +203,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>169-V,V,M,C,K,Y,P,F,L,I-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>170-M,C,M,C,K,C,C,C,C,C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -843,423 +349,730 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>第十一轮迭代</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第十二轮迭代-去掉Ton低的序列</t>
+    <t>207-M,T,L,M,C,L,M,M,K,M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>208-D,C,T,C,E,P,C,K,C,K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>209-T,C,T,L,M,T,L,M,M,K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>210-V,C,A,C,M,H,A,C,T,K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>211-K,S,M,M,M,M,M,M,M,M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>169-M,M,C,M,K,C,M,C,M,M</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对位选择性</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>间位选择性</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>邻位选择性</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第二轮迭代</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第三轮随机</t>
+      <t>para</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>-</t>
+      <t>-Hydroxyacetophenone Selectivity(%)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>meta</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="宋体"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
         <family val="1"/>
-        <charset val="134"/>
       </rPr>
-      <t>随机</t>
+      <t>-Hydroxyacetophenone Selectivity</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
+        <i/>
         <sz val="11"/>
-        <rFont val="宋体"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
         <family val="1"/>
-        <charset val="134"/>
       </rPr>
-      <t>第四轮迭代</t>
+      <t>(%)</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第五轮迭代</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第七轮迭代</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>第十三轮迭代</t>
+      <t>ortho</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>-</t>
+      <t>-Hydroxyacetophenone Selectivity(%)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模型</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>第十四轮迭代</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模型</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>第十五轮迭代</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模型</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>第十六轮迭代</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模型</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>第十七轮迭代</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模型</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>第十八轮迭代</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模型-K打乱</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>207-M,T,L,M,C,L,M,M,K,M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>208-D,C,T,C,E,P,C,K,C,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>209-T,C,T,L,M,T,L,M,M,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>210-V,C,A,C,M,H,A,C,T,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>211-K,S,M,M,M,M,M,M,M,M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>212-T,C,T,L,M,T,L,M,M,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>213-C,K,T,G,S,S,C,S,C,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>214-K,M,M,M,M,M,M,M,M,S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>215-M,K,M,M,K,M,K,M,M,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>216-T,T,L,M,L,M,C,M,T,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>第十九轮迭代</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模型-K打乱</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>217-Y,M,M,K,M,K,M,M,M,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>218-G,M,M,K,K,C,M,P,M,L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>219-C,M,C,L,P,K,P,P,P,R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>220-G,L,M,K,K,M,M,P,L,M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>221-C,M,C,P,P,P,P,P,L,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>222-K,L,L,P,M,L,P,G,M,L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>223-C,C,H,P,C,K,P,P,L,L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>224-C,M,G,L,L,P,K,L,M,P</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>225-K,C,C,P,H,P,H,P,P,R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>第二十轮迭代</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模型-K打乱</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>226-W,M,M,Q,K,T,T,K,M,M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>227-Y,W,K,M,T,M,K,M,T,Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>228-K,M,M,L,M,M,L,M,M,S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>229-P,T,K,K,M,T,M,M,W,W</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>230-L,K,I,W,M,K,M,T,T,M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>231-P,K,K,T,T,K,M,M,M,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>232-F,C,M,M,G,M,M,M,G,K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>233-L,K,T,W,K,M,K,M,T,M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>234-K,F,G,G,C,G,G,C,G,G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21-D,E,T,W,K,I,Q,D,C,M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>22-A,P,M,F,K,D,V,H,W,P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>23-W,T,G,S,K,D,T,C,Q,N</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>24-M,V,M,C,K,R,P,F,P,P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>25-L,V,N,I,K,G,H,F,P,P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26-F,P,N,C,K,S,M,C,C,V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>27-P,Q,G,G,K,D,D,H,Q,N</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>28-T,C,V,D,K,F,S,N,Y,D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>29-P,Q,G,I,K,D,D,C,Q,L</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30-P,V,M,C,K,Y,P,F,A,P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>31-G,V,M,C,K,G,P,F,L,P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>32-T,R,V,D,K,F,S,N,Y,D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>33-N,Q,F,L,K,H,D,C,D,I</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>34-S,V,M,C,K,G,P,W,P,P</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>35-P,P,H,C,K,S,Y,I,E,S</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>36-A,Q,M,L,K,H,T,C,M,G</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>37-D,E,T,I,K,I,W,Y,A,M</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>38-M,T,G,A,K,D,D,C,Q,T</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>39-V,D,V,D,K,F,S,F,L,D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>40-I,F,Y,I,K,V,A,N,M,D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>61-F,P,N,W,K,S,M,D,C,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62-A,V,H,C,K,S,V,I,W,S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>63-W,E,T,S,K,I,T,Y,A,M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>64-S,V,M,C,K,R,P,W,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65-L,V,N,I,K,G,H,W,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>66-F,V,M,C,K,S,P,F,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>67-W,Q,G,S,K,D,T,H,Q,N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68-P,C,N,C,K,H,M,C,C,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>69-W,Q,G,I,K,D,T,C,Q,L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70-P,V,M,C,K,Y,P,W,A,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>71-G,V,M,C,K,G,P,W,L,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>72-P,R,N,C,K,H,M,C,C,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>73-M,V,M,C,K,G,P,F,P,I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>74-G,P,M,C,K,G,Y,F,L,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75-A,V,M,C,K,G,T,F,M,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>76-F,P,N,C,K,S,W,C,C,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>77-M,E,T,A,K,I,W,Y,A,T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78-V,P,N,C,K,H,M,F,L,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>79-W,T,G,I,K,D,T,C,Q,N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80-D,E,S,T,K,I,Q,Y,V,M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>81-F,P,N,W,K,S,W,D,C,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>82-A,P,N,C,K,H,V,F,W,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>83-W,E,T,S,K,I,T,Y,A,T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>84-G,V,M,C,K,R,P,W,L,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85-L,V,N,I,K,G,H,W,L,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>86-F,V,M,C,K,S,T,F,M,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>87-M,Q,T,A,K,I,W,H,A,T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>88-V,C,N,C,K,H,M,F,L,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>89-M,Q,T,I,K,I,W,Y,A,L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90-V,R,N,C,K,H,M,F,L,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101-G,V,M,S,K,G,T,F,L,Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102-P,R,M,I,K,G,T,F,M,L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103-F,Q,S,T,K,S,Y,H,V,I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>104-S,V,M,S,K,G,T,W,M,Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>105-A,P,I,C,K,S,Y,C,W,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>106-A,Q,M,T,K,S,T,H,M,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>107-M,P,I,A,K,S,V,C,W,T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>108-V,V,M,C,K,Y,P,F,L,I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>109-S,P,M,I,K,G,Y,D,C,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>110-S,P,S,T,K,G,Y,D,V,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111-G,V,M,W,K,G,T,D,C,Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>112-A,Q,M,T,K,S,V,H,W,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>113-W,Q,S,S,K,S,T,H,V,I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114-P,R,M,I,K,R,T,F,M,L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>115-L,Q,N,I,K,S,H,H,M,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>116-F,P,I,A,K,S,V,C,W,T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117-S,Q,M,I,K,G,Y,H,C,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>118-P,C,M,I,K,G,T,F,M,L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>119-S,Q,M,I,K,G,Y,D,C,L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120-P,V,M,S,K,Y,T,F,A,Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>121-M,V,M,W,K,G,I,F,C,I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>122-A,P,M,V,K,W,D,F,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>123-F,V,C,C,K,I,S,R,P,G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>124-F,R,N,C,K,S,M,I,C,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>125-F,V,M,T,K,L,P,N,I,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>126-M,V,M,C,K,F,P,F,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>127-M,V,M,C,K,G,Q,H,P,I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>128-Q,V,Q,W,K,S,P,F,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>129-S,V,M,C,K,Q,P,I,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>130-T,L,M,P,K,G,Y,F,C,I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>131-Q,V,Q,W,K,S,I,F,C,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>132-Q,V,C,W,K,I,S,R,P,G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>133-S,R,M,C,K,Q,P,I,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>134-M,V,M,T,K,L,P,N,I,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>135-F,V,M,T,K,F,P,N,I,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>136-S,V,M,C,K,Q,Q,H,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>137-Q,P,Q,W,K,W,D,F,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>138-M,V,M,C,K,Q,P,I,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>139-T,L,M,P,K,Q,Y,I,C,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>140-A,P,M,V,K,W,D,Y,P,C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>141-F,V,M,W,K,F,I,N,C,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>142-A,P,M,V,K,W,D,N,I,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>143-S,R,C,C,K,I,S,R,P,G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>144-A,R,M,V,K,W,D,I,P,C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>145-T,L,M,T,K,L,Y,N,I,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>146-S,V,M,C,K,F,Q,H,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>147-Q,P,Q,W,K,W,Q,H,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>148-Q,V,Q,W,K,L,P,N,I,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>149-S,V,M,C,K,Q,Q,I,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>150-T,L,Q,P,K,W,Y,F,C,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>151-A,R,M,C,K,W,L,I,M,C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>152-F,L,Q,R,K,W,C,V,C,C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>153-F,R,M,W,K,V,G,N,C,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>154-Q,S,V,M,K,W,Q,H,P,G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>155-T,L,M,T,K,L,Y,P,R,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>156-T,L,M,C,K,R,Q,I,P,G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>157-T,L,C,T,K,L,Y,N,I,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>158-C,G,C,C,K,G,S,R,G,S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>159-Q,F,Q,W,K,W,Q,H,P,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>160-F,R,S,W,K,C,L,N,L,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Batch 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>212-C,K,T,G,S,S,C,S,C,K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>213-K,M,M,M,M,M,M,M,M,S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>214-M,K,M,M,K,M,K,M,M,K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>215-T,T,L,M,L,M,C,M,T,K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>216-Y,M,M,K,M,K,M,M,M,K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>217-G,M,M,K,K,C,M,P,M,L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>218-C,M,C,L,P,K,P,P,P,R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>219-G,L,M,K,K,M,M,P,L,M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220-C,M,C,P,P,P,P,P,L,K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>221-K,L,L,P,M,L,P,G,M,L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>222-C,C,H,P,C,K,P,P,L,L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>223-C,M,G,L,L,P,K,L,M,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>224-K,C,C,P,H,P,H,P,P,R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>225-W,M,M,Q,K,T,T,K,M,M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>226-Y,W,K,M,T,M,K,M,T,Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>227-K,M,M,L,M,M,L,M,M,S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>228-P,T,K,K,M,T,M,M,W,W</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>229-L,K,I,W,M,K,M,T,T,M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>230-P,K,K,T,T,K,M,M,M,K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>231-F,C,M,M,G,M,M,M,G,K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>232-L,K,T,W,K,M,K,M,T,M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>233-K,F,G,G,C,G,G,C,G,G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>91-S,P,M,W,K,G,Y,D,C,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>92-A,P,I,C,K,S,V,C,W,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>93-W,V,M,S,K,G,T,F,M,Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>94-M,V,M,C,K,R,P,F,P,I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>95-L,V,N,I,K,G,H,F,P,I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>96-F,Q,S,T,K,S,Y,H,V,P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>97-P,Q,M,C,K,G,T,H,M,Q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>98-R,C,I,C,K,S,W,C,C,V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99-P,Q,M,I,K,G,T,F,M,L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100-P,V,M,C,K,Y,P,F,A,L</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1267,10 +1080,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1302,25 +1116,20 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
-      <family val="1"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1345,7 +1154,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1355,16 +1164,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1855,38 +1666,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I274"/>
+  <dimension ref="A1:I273"/>
   <sheetFormatPr defaultColWidth="10.25" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="28" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="10.25" style="2"/>
+    <col min="2" max="4" width="10.25" style="2"/>
+    <col min="5" max="5" width="10.25" style="7"/>
+    <col min="6" max="16384" width="10.25" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
-        <v>101</v>
+      <c r="A2" s="7" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1">
         <v>20.475292612196831</v>
@@ -1897,7 +1710,7 @@
       <c r="D3" s="1">
         <v>46.250435714271589</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="7">
         <v>6.9690000000000003</v>
       </c>
       <c r="G3" s="1"/>
@@ -1906,7 +1719,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1">
         <v>21.367940435199319</v>
@@ -1917,7 +1730,7 @@
       <c r="D4" s="1">
         <v>47.177505235880872</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="7">
         <v>4.4550000000000001</v>
       </c>
       <c r="F4" s="1"/>
@@ -1935,7 +1748,7 @@
       <c r="D5" s="1">
         <v>45.490179620614398</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="7">
         <v>2.7210000000000001</v>
       </c>
       <c r="F5" s="1"/>
@@ -1953,7 +1766,7 @@
       <c r="D6" s="1">
         <v>47.543416622363992</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="7">
         <v>12.690000000000001</v>
       </c>
       <c r="F6" s="1"/>
@@ -1971,7 +1784,7 @@
       <c r="D7" s="1">
         <v>47.702311786903934</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="7">
         <v>4.2670000000000003</v>
       </c>
     </row>
@@ -1988,7 +1801,7 @@
       <c r="D8" s="1">
         <v>45.542025022737654</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="7">
         <v>2.786</v>
       </c>
     </row>
@@ -2005,7 +1818,7 @@
       <c r="D9" s="1">
         <v>47.002985157906494</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="7">
         <v>6.4669999999999987</v>
       </c>
     </row>
@@ -2022,7 +1835,7 @@
       <c r="D10" s="1">
         <v>47.210260800953563</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="7">
         <v>8.8469999999999995</v>
       </c>
     </row>
@@ -2039,7 +1852,7 @@
       <c r="D11" s="1">
         <v>44.870496603032642</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="7">
         <v>3.0430000000000001</v>
       </c>
     </row>
@@ -2056,7 +1869,7 @@
       <c r="D12" s="1">
         <v>46.780417953845614</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="7">
         <v>8.7949999999999999</v>
       </c>
     </row>
@@ -2073,7 +1886,7 @@
       <c r="D13" s="1">
         <v>49.098080083788886</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="7">
         <v>14.447999999999999</v>
       </c>
     </row>
@@ -2090,7 +1903,7 @@
       <c r="D14" s="1">
         <v>49.910104794817471</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="7">
         <v>10.827999999999999</v>
       </c>
     </row>
@@ -2107,7 +1920,7 @@
       <c r="D15" s="1">
         <v>49.784262152785615</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="7">
         <v>14.584999999999999</v>
       </c>
     </row>
@@ -2124,7 +1937,7 @@
       <c r="D16" s="1">
         <v>48.836309742556075</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="7">
         <v>10.085000000000001</v>
       </c>
     </row>
@@ -2141,7 +1954,7 @@
       <c r="D17" s="1">
         <v>47.608149022588975</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="7">
         <v>7.12</v>
       </c>
     </row>
@@ -2158,7 +1971,7 @@
       <c r="D18" s="1">
         <v>48.816489846452839</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="7">
         <v>15.615</v>
       </c>
     </row>
@@ -2175,7 +1988,7 @@
       <c r="D19" s="1">
         <v>44.127391694701501</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="7">
         <v>2.488</v>
       </c>
     </row>
@@ -2192,7 +2005,7 @@
       <c r="D20" s="1">
         <v>44.118127968249482</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="7">
         <v>2.4990000000000001</v>
       </c>
     </row>
@@ -2209,7 +2022,7 @@
       <c r="D21" s="1">
         <v>46.955676935866521</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="7">
         <v>5.6199999999999992</v>
       </c>
     </row>
@@ -2226,29 +2039,29 @@
       <c r="D22" s="1">
         <v>47.286317842053947</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="7">
         <v>3.9630000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
-        <v>218</v>
+      <c r="A24" s="7" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="4">
+        <v>98</v>
+      </c>
+      <c r="B25" s="3">
         <v>20.187353316705973</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>31.318376027300019</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>48.494270655994015</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="8">
         <v>11.843</v>
       </c>
       <c r="G25" s="1"/>
@@ -2257,359 +2070,359 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="4">
+        <v>99</v>
+      </c>
+      <c r="B26" s="3">
         <v>21.111238848457454</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="3">
         <v>30.124149146510725</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="3">
         <v>48.764612005031822</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="8">
         <v>8.3219999999999992</v>
       </c>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="4">
+        <v>100</v>
+      </c>
+      <c r="B27" s="3">
         <v>20.56152549687711</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="3">
         <v>30.247470426773752</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>49.191004076349145</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="8">
         <v>12.315</v>
       </c>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="4">
+        <v>101</v>
+      </c>
+      <c r="B28" s="3">
         <v>20.850142389078158</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="3">
         <v>29.288683201849054</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>49.861174409072795</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="8">
         <v>17.869</v>
       </c>
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="4">
+        <v>102</v>
+      </c>
+      <c r="B29" s="3">
         <v>22.485670370586124</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="3">
         <v>27.51497435654715</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="3">
         <v>49.999355272866723</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="8">
         <v>7.2619999999999996</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="4">
+        <v>103</v>
+      </c>
+      <c r="B30" s="3">
         <v>20.869008458213408</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="3">
         <v>28.94853109490451</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>50.182460446882089</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="8">
         <v>16.795999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="4">
+        <v>104</v>
+      </c>
+      <c r="B31" s="3">
         <v>23.177666721441803</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="3">
         <v>28.061117914162715</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="3">
         <v>48.761215364395483</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="8">
         <v>3.6140000000000008</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="4">
+        <v>105</v>
+      </c>
+      <c r="B32" s="3">
         <v>20.892345133907305</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="3">
         <v>30.982608696150514</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>48.125046169942181</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="8">
         <v>8.3559999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="4">
+        <v>106</v>
+      </c>
+      <c r="B33" s="3">
         <v>21.579070543805834</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="3">
         <v>28.282885299106809</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="3">
         <v>50.138044157087364</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="8">
         <v>7.7379999999999995</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" s="4">
+        <v>107</v>
+      </c>
+      <c r="B34" s="3">
         <v>20.650439869683503</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="3">
         <v>29.531104866731425</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="3">
         <v>49.818455263585079</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="8">
         <v>14.733000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="4">
+        <v>108</v>
+      </c>
+      <c r="B35" s="3">
         <v>20.667377684898714</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="3">
         <v>29.149757509542091</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="3">
         <v>50.182864805559205</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="8">
         <v>17.577999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="4">
+        <v>109</v>
+      </c>
+      <c r="B36" s="3">
         <v>22.207721833554807</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="3">
         <v>29.689433837515306</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="3">
         <v>48.102844328929876</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="8">
         <v>4.4380000000000006</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="4">
+        <v>110</v>
+      </c>
+      <c r="B37" s="3">
         <v>21.668385746723857</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="3">
         <v>30.663027689556401</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="3">
         <v>47.668586563719742</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="8">
         <v>5.8859999999999992</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B38" s="4">
+        <v>111</v>
+      </c>
+      <c r="B38" s="3">
         <v>20.918034204766787</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="3">
         <v>28.842519029571775</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="3">
         <v>50.239446765661434</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="8">
         <v>19.193999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="4">
+        <v>112</v>
+      </c>
+      <c r="B39" s="3">
         <v>20.751792269516436</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="3">
         <v>30.155185108200428</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="3">
         <v>49.093022622283144</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="8">
         <v>10.402999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="4">
+        <v>113</v>
+      </c>
+      <c r="B40" s="3">
         <v>20.78612858334478</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="3">
         <v>29.609871371326665</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="3">
         <v>49.604000045328561</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="8">
         <v>12.007</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="4">
+        <v>114</v>
+      </c>
+      <c r="B41" s="3">
         <v>20.202279340903747</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="3">
         <v>31.416349251940584</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="3">
         <v>48.381371407155669</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="8">
         <v>12.085000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B42" s="4">
+        <v>115</v>
+      </c>
+      <c r="B42" s="3">
         <v>20.222432970025586</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="3">
         <v>30.757369798184026</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="3">
         <v>49.020197231790391</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="8">
         <v>11.779</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="4">
+        <v>116</v>
+      </c>
+      <c r="B43" s="3">
         <v>21.979436708935005</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="3">
         <v>32.701263357927949</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="3">
         <v>45.319299933137046</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="8">
         <v>2.024</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="4">
+        <v>117</v>
+      </c>
+      <c r="B44" s="3">
         <v>20.829768471098596</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="3">
         <v>32.944220176116062</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="3">
         <v>46.226011352785342</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="8">
         <v>4.681</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="8"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
+      <c r="A46" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="8"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="4">
+        <v>19</v>
+      </c>
+      <c r="B47" s="3">
         <v>21.281687676047206</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="3">
         <v>32.949650704615657</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="3">
         <v>45.768661619337145</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="8">
         <v>3.4959999999999996</v>
       </c>
       <c r="G47" s="1"/>
@@ -2618,359 +2431,359 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="4">
+        <v>20</v>
+      </c>
+      <c r="B48" s="3">
         <v>20.4911960296191</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="3">
         <v>32.102853528091075</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="3">
         <v>47.405950442289836</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="8">
         <v>8.1069999999999993</v>
       </c>
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="4">
+        <v>21</v>
+      </c>
+      <c r="B49" s="3">
         <v>20.623377271314503</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="3">
         <v>31.499199043706724</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="3">
         <v>47.877423684978766</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="8">
         <v>6.89</v>
       </c>
       <c r="F49" s="1"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="4">
+        <v>22</v>
+      </c>
+      <c r="B50" s="3">
         <v>21.680853893728802</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="3">
         <v>29.465983906364301</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="3">
         <v>48.853162199906897</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="8">
         <v>5.3740000000000006</v>
       </c>
       <c r="F50" s="1"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="4">
+        <v>23</v>
+      </c>
+      <c r="B51" s="3">
         <v>19.699774686019779</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="3">
         <v>32.168654113414412</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="3">
         <v>48.131571200565801</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="8">
         <v>11.339000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="4">
+        <v>24</v>
+      </c>
+      <c r="B52" s="3">
         <v>22.048518985408581</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="3">
         <v>31.456113148841773</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="3">
         <v>46.495367865749643</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E52" s="8">
         <v>2.8080000000000003</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="4">
+        <v>25</v>
+      </c>
+      <c r="B53" s="3">
         <v>19.652186934541628</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="3">
         <v>31.684596356471715</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="3">
         <v>48.66321670898666</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="8">
         <v>13.763999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="4">
+        <v>26</v>
+      </c>
+      <c r="B54" s="3">
         <v>19.04520111509359</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="3">
         <v>34.308376476835257</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="3">
         <v>46.64642240807116</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="8">
         <v>1.1059999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="4">
+        <v>27</v>
+      </c>
+      <c r="B55" s="3">
         <v>20.471165600315604</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="3">
         <v>30.322294441012353</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="3">
         <v>49.206539958672039</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="8">
         <v>9.0040000000000013</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56" s="4">
+        <v>28</v>
+      </c>
+      <c r="B56" s="3">
         <v>19.624830223819902</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="3">
         <v>33.572883795829398</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="3">
         <v>46.802285980350689</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="8">
         <v>7.9440000000000008</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57" s="4">
+        <v>29</v>
+      </c>
+      <c r="B57" s="3">
         <v>19.750458092270996</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="3">
         <v>32.525434126056489</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="3">
         <v>47.724107781672529</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="8">
         <v>8.1389999999999993</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B58" s="4">
+        <v>30</v>
+      </c>
+      <c r="B58" s="3">
         <v>19.768538164626698</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="3">
         <v>31.927225728410967</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="3">
         <v>48.304236106962335</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E58" s="8">
         <v>11.436</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="4">
+        <v>31</v>
+      </c>
+      <c r="B59" s="3">
         <v>20.249698023132851</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="3">
         <v>29.880230891197382</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="3">
         <v>49.870071085669778</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E59" s="8">
         <v>20.04</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="4">
+        <v>32</v>
+      </c>
+      <c r="B60" s="3">
         <v>21.856722580947036</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="3">
         <v>31.381451197828937</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="3">
         <v>46.761826221224041</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E60" s="8">
         <v>3.3079999999999998</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B61" s="4">
+        <v>33</v>
+      </c>
+      <c r="B61" s="3">
         <v>18.59338529968732</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="3">
         <v>32.721973714839351</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="3">
         <v>48.684640985473322</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E61" s="8">
         <v>3.0049999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B62" s="4">
+        <v>34</v>
+      </c>
+      <c r="B62" s="3">
         <v>20.436311449195511</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="3">
         <v>31.990033380668237</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="3">
         <v>47.573655170136256</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E62" s="8">
         <v>6.0689999999999991</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="4">
+        <v>35</v>
+      </c>
+      <c r="B63" s="3">
         <v>19.843047127077462</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="3">
         <v>31.930400615486072</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="3">
         <v>48.226552257436467</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E63" s="8">
         <v>9.9039999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64" s="4">
+        <v>36</v>
+      </c>
+      <c r="B64" s="3">
         <v>20.645830717082056</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="3">
         <v>30.767703927006298</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="3">
         <v>48.586465355911642</v>
       </c>
-      <c r="E64" s="4">
+      <c r="E64" s="8">
         <v>6.9750000000000005</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="4">
+        <v>37</v>
+      </c>
+      <c r="B65" s="3">
         <v>20.099393310443958</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="3">
         <v>31.677328149261474</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="3">
         <v>48.223278540294572</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E65" s="8">
         <v>9.0450000000000017</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="4">
+        <v>38</v>
+      </c>
+      <c r="B66" s="3">
         <v>19.928234293714823</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="3">
         <v>31.366846932161476</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="3">
         <v>48.704918774123698</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E66" s="8">
         <v>15.019</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="8"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
+      <c r="A68" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="8"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="4">
+        <v>120</v>
+      </c>
+      <c r="B69" s="3">
         <v>19.736707449696148</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="3">
         <v>33.964869291093265</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="3">
         <v>46.29842325921058</v>
       </c>
-      <c r="E69" s="4">
+      <c r="E69" s="8">
         <v>7.415</v>
       </c>
       <c r="G69" s="1"/>
@@ -2979,359 +2792,359 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="4">
+        <v>121</v>
+      </c>
+      <c r="B70" s="3">
         <v>20.263105658215164</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="3">
         <v>31.070141499527921</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="3">
         <v>48.666752842256912</v>
       </c>
-      <c r="E70" s="4">
+      <c r="E70" s="8">
         <v>10.562000000000001</v>
       </c>
       <c r="F70" s="1"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="4">
+        <v>122</v>
+      </c>
+      <c r="B71" s="3">
         <v>19.23558567187051</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="3">
         <v>36.865865338569101</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71" s="3">
         <v>43.898548989560382</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E71" s="8">
         <v>2.9009999999999998</v>
       </c>
       <c r="F71" s="1"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B72" s="4">
+        <v>123</v>
+      </c>
+      <c r="B72" s="3">
         <v>19.68531531697376</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="3">
         <v>32.598492208663409</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72" s="3">
         <v>47.716192474362835</v>
       </c>
-      <c r="E72" s="4">
+      <c r="E72" s="8">
         <v>9.6739999999999995</v>
       </c>
       <c r="F72" s="1"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" s="4">
+        <v>124</v>
+      </c>
+      <c r="B73" s="3">
         <v>22.431279786266401</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="3">
         <v>27.324451899682554</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D73" s="3">
         <v>50.244268314051041</v>
       </c>
-      <c r="E73" s="4">
+      <c r="E73" s="8">
         <v>5.8390000000000004</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" s="4">
+        <v>125</v>
+      </c>
+      <c r="B74" s="3">
         <v>20.167315729531921</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="3">
         <v>30.46828408555298</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="3">
         <v>49.364400184915098</v>
       </c>
-      <c r="E74" s="4">
+      <c r="E74" s="8">
         <v>18.331</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" s="4">
+        <v>126</v>
+      </c>
+      <c r="B75" s="3">
         <v>22.17668488160291</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="3">
         <v>30.908803145408498</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75" s="3">
         <v>46.914511972988578</v>
       </c>
-      <c r="E75" s="4">
+      <c r="E75" s="8">
         <v>3.3090000000000002</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B76" s="4">
+        <v>127</v>
+      </c>
+      <c r="B76" s="3">
         <v>20.222623693078198</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="3">
         <v>30.727953217544151</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76" s="3">
         <v>49.049423089377655</v>
       </c>
-      <c r="E76" s="4">
+      <c r="E76" s="8">
         <v>13.209999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B77" s="4">
+        <v>128</v>
+      </c>
+      <c r="B77" s="3">
         <v>21.090372430984431</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="3">
         <v>32.944042324612738</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77" s="3">
         <v>45.965585244402831</v>
       </c>
-      <c r="E77" s="4">
+      <c r="E77" s="8">
         <v>4.0009999999999994</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B78" s="4">
+        <v>129</v>
+      </c>
+      <c r="B78" s="3">
         <v>20.628295280767187</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="3">
         <v>32.426011347653699</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D78" s="3">
         <v>46.945693371579111</v>
       </c>
-      <c r="E78" s="4">
+      <c r="E78" s="8">
         <v>5.8230000000000004</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B79" s="4">
+        <v>130</v>
+      </c>
+      <c r="B79" s="3">
         <v>20.318162842361083</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="3">
         <v>31.173882900210227</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D79" s="3">
         <v>48.507954257428693</v>
       </c>
-      <c r="E79" s="6">
+      <c r="E79" s="8">
         <v>11.584999999999999</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B80" s="4">
+        <v>131</v>
+      </c>
+      <c r="B80" s="3">
         <v>20.486438285697936</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80" s="3">
         <v>31.071088689580424</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80" s="3">
         <v>48.442473024721643</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E80" s="8">
         <v>9.5459999999999994</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B81" s="4">
+        <v>132</v>
+      </c>
+      <c r="B81" s="3">
         <v>21.028702717939744</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81" s="3">
         <v>29.415187539745986</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81" s="3">
         <v>49.556109742314277</v>
       </c>
-      <c r="E81" s="6">
+      <c r="E81" s="8">
         <v>19.286999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B82" s="4">
+        <v>133</v>
+      </c>
+      <c r="B82" s="3">
         <v>20.148503084995831</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82" s="3">
         <v>31.460092973000748</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82" s="3">
         <v>48.391403942003414</v>
       </c>
-      <c r="E82" s="6">
+      <c r="E82" s="8">
         <v>12.283000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B83" s="4">
+        <v>134</v>
+      </c>
+      <c r="B83" s="3">
         <v>20.147658431086718</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83" s="3">
         <v>31.362019757885925</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83" s="3">
         <v>48.49032181102735</v>
       </c>
-      <c r="E83" s="6">
+      <c r="E83" s="8">
         <v>16.389000000000003</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B84" s="4">
+        <v>135</v>
+      </c>
+      <c r="B84" s="3">
         <v>19.012105777723626</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="3">
         <v>36.553611834430853</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84" s="3">
         <v>44.434282387845521</v>
       </c>
-      <c r="E84" s="6">
+      <c r="E84" s="8">
         <v>6.7910000000000004</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B85" s="4">
+        <v>136</v>
+      </c>
+      <c r="B85" s="3">
         <v>18.987985890104959</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85" s="3">
         <v>38.346938687503773</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85" s="3">
         <v>42.665075422391268</v>
       </c>
-      <c r="E85" s="6">
+      <c r="E85" s="8">
         <v>1.927</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B86" s="4">
+        <v>137</v>
+      </c>
+      <c r="B86" s="3">
         <v>20.398870400677346</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86" s="3">
         <v>32.465099640486386</v>
       </c>
-      <c r="D86" s="4">
+      <c r="D86" s="3">
         <v>47.136029958836275</v>
       </c>
-      <c r="E86" s="6">
+      <c r="E86" s="8">
         <v>7.8239999999999998</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B87" s="4">
+        <v>138</v>
+      </c>
+      <c r="B87" s="3">
         <v>20.185375635016204</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87" s="3">
         <v>36.194976029161225</v>
       </c>
-      <c r="D87" s="4">
+      <c r="D87" s="3">
         <v>43.619648335822575</v>
       </c>
-      <c r="E87" s="6">
+      <c r="E87" s="8">
         <v>2.1550000000000002</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B88" s="4">
+        <v>139</v>
+      </c>
+      <c r="B88" s="3">
         <v>17.482931411249162</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88" s="3">
         <v>38.088667388612663</v>
       </c>
-      <c r="D88" s="4">
+      <c r="D88" s="3">
         <v>44.428401200138183</v>
       </c>
-      <c r="E88" s="4">
+      <c r="E88" s="8">
         <v>1.018</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="8"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A90" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
+      <c r="A90" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="9"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B91" s="4">
+        <v>140</v>
+      </c>
+      <c r="B91" s="3">
         <v>21.072222900275271</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91" s="3">
         <v>34.49953118237822</v>
       </c>
-      <c r="D91" s="4">
+      <c r="D91" s="3">
         <v>44.428245917346509</v>
       </c>
-      <c r="E91" s="6">
+      <c r="E91" s="8">
         <v>3.556</v>
       </c>
       <c r="G91" s="1"/>
@@ -3340,189 +3153,189 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B92" s="4">
+        <v>141</v>
+      </c>
+      <c r="B92" s="3">
         <v>21.031220900011917</v>
       </c>
-      <c r="C92" s="4">
+      <c r="C92" s="3">
         <v>30.049357086817164</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D92" s="3">
         <v>48.919422013170916</v>
       </c>
-      <c r="E92" s="6">
+      <c r="E92" s="8">
         <v>11.052</v>
       </c>
       <c r="F92" s="1"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B93" s="4">
+        <v>142</v>
+      </c>
+      <c r="B93" s="3">
         <v>20.418688479879222</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93" s="3">
         <v>32.528240064168301</v>
       </c>
-      <c r="D93" s="4">
+      <c r="D93" s="3">
         <v>47.053071455952484</v>
       </c>
-      <c r="E93" s="6">
+      <c r="E93" s="8">
         <v>8.657</v>
       </c>
       <c r="F93" s="1"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B94" s="4">
+        <v>143</v>
+      </c>
+      <c r="B94" s="3">
         <v>20.263568468262584</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94" s="3">
         <v>30.702173627005813</v>
       </c>
-      <c r="D94" s="4">
+      <c r="D94" s="3">
         <v>49.034257904731597</v>
       </c>
-      <c r="E94" s="6">
+      <c r="E94" s="8">
         <v>10.882000000000001</v>
       </c>
       <c r="F94" s="1"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B95" s="4">
+        <v>144</v>
+      </c>
+      <c r="B95" s="3">
         <v>22.143668068046757</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95" s="3">
         <v>29.436387987156976</v>
       </c>
-      <c r="D95" s="4">
+      <c r="D95" s="3">
         <v>48.419943944796273</v>
       </c>
-      <c r="E95" s="6">
+      <c r="E95" s="8">
         <v>4.7509999999999994</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B96" s="4">
+        <v>145</v>
+      </c>
+      <c r="B96" s="3">
         <v>20.607088804352557</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96" s="3">
         <v>29.934723725906924</v>
       </c>
-      <c r="D96" s="4">
+      <c r="D96" s="3">
         <v>49.458187469740523</v>
       </c>
-      <c r="E96" s="6">
+      <c r="E96" s="8">
         <v>17.045999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B97" s="4">
+        <v>146</v>
+      </c>
+      <c r="B97" s="3">
         <v>20.751821106662</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97" s="3">
         <v>31.407442278303879</v>
       </c>
-      <c r="D97" s="4">
+      <c r="D97" s="3">
         <v>47.840736615034118</v>
       </c>
-      <c r="E97" s="6">
+      <c r="E97" s="8">
         <v>8.6029999999999998</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B98" s="4">
+        <v>147</v>
+      </c>
+      <c r="B98" s="3">
         <v>20.183656846412546</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98" s="3">
         <v>31.593277099289899</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98" s="3">
         <v>48.223066054297561</v>
       </c>
-      <c r="E98" s="6">
+      <c r="E98" s="8">
         <v>11.875999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B99" s="4">
+        <v>148</v>
+      </c>
+      <c r="B99" s="3">
         <v>19.112668851775346</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99" s="3">
         <v>37.747983227227408</v>
       </c>
-      <c r="D99" s="4">
+      <c r="D99" s="3">
         <v>43.139347920997253</v>
       </c>
-      <c r="E99" s="6">
+      <c r="E99" s="8">
         <v>3.1340000000000003</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B100" s="4">
+        <v>149</v>
+      </c>
+      <c r="B100" s="3">
         <v>20.525967091642151</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100" s="3">
         <v>33.238073444480769</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D100" s="3">
         <v>46.23595946387708</v>
       </c>
-      <c r="E100" s="6">
+      <c r="E100" s="8">
         <v>5.2469999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="6"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="8"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="6"/>
+      <c r="A102" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="8"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B103" s="4">
+      <c r="A103" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B103" s="3">
         <v>20.869015809178791</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103" s="3">
         <v>34.427671996379914</v>
       </c>
-      <c r="D103" s="4">
+      <c r="D103" s="3">
         <v>44.703312194441295</v>
       </c>
-      <c r="E103" s="6">
+      <c r="E103" s="8">
         <v>3.5030000000000001</v>
       </c>
       <c r="G103" s="1"/>
@@ -3530,175 +3343,175 @@
       <c r="I103" s="1"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B104" s="4">
+      <c r="A104" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B104" s="3">
         <v>20.004059665943238</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104" s="3">
         <v>33.031779084819028</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D104" s="3">
         <v>46.964161249237726</v>
       </c>
-      <c r="E104" s="6">
+      <c r="E104" s="8">
         <v>8.0380000000000003</v>
       </c>
       <c r="F104" s="1"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B105" s="4">
+      <c r="A105" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B105" s="3">
         <v>20.692905948306528</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="3">
         <v>35.0642488254272</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D105" s="3">
         <v>44.242845226266262</v>
       </c>
-      <c r="E105" s="6">
+      <c r="E105" s="8">
         <v>3.6140000000000003</v>
       </c>
       <c r="F105" s="1"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B106" s="4">
+      <c r="A106" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="B106" s="3">
         <v>19.827867468738546</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106" s="3">
         <v>32.804221170909656</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D106" s="3">
         <v>47.367911360351798</v>
       </c>
-      <c r="E106" s="6">
+      <c r="E106" s="8">
         <v>11.02</v>
       </c>
       <c r="F106" s="1"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B107" s="4">
+      <c r="A107" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B107" s="3">
         <v>22.574725748275426</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107" s="3">
         <v>28.463172396008289</v>
       </c>
-      <c r="D107" s="4">
+      <c r="D107" s="3">
         <v>48.962101855716277</v>
       </c>
-      <c r="E107" s="6">
+      <c r="E107" s="8">
         <v>5.9489999999999998</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B108" s="4">
+      <c r="A108" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="B108" s="3">
         <v>22.296197662376095</v>
       </c>
-      <c r="C108" s="4">
+      <c r="C108" s="3">
         <v>31.771313462392023</v>
       </c>
-      <c r="D108" s="4">
+      <c r="D108" s="3">
         <v>45.932488875231883</v>
       </c>
-      <c r="E108" s="6">
+      <c r="E108" s="8">
         <v>2.9059999999999997</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B109" s="4">
+      <c r="A109" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B109" s="3">
         <v>20.688633158228239</v>
       </c>
-      <c r="C109" s="4">
+      <c r="C109" s="3">
         <v>32.222498141891236</v>
       </c>
-      <c r="D109" s="4">
+      <c r="D109" s="3">
         <v>47.088868699880535</v>
       </c>
-      <c r="E109" s="6">
+      <c r="E109" s="8">
         <v>6.1</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B110" s="4">
+      <c r="A110" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B110" s="3">
         <v>18.905216610630781</v>
       </c>
-      <c r="C110" s="4">
+      <c r="C110" s="3">
         <v>37.39274937683124</v>
       </c>
-      <c r="D110" s="4">
+      <c r="D110" s="3">
         <v>43.702034012537979</v>
       </c>
-      <c r="E110" s="6">
+      <c r="E110" s="8">
         <v>3.9689999999999999</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B111" s="4">
+      <c r="A111" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B111" s="3">
         <v>20.165691656113907</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111" s="3">
         <v>33.426878381373662</v>
       </c>
-      <c r="D111" s="4">
+      <c r="D111" s="3">
         <v>46.407429962512438</v>
       </c>
-      <c r="E111" s="6">
+      <c r="E111" s="8">
         <v>7.024</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B112" s="4">
+      <c r="A112" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="B112" s="3">
         <v>19.734492572569209</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112" s="3">
         <v>33.777709745374324</v>
       </c>
-      <c r="D112" s="4">
+      <c r="D112" s="3">
         <v>46.48779768205646</v>
       </c>
-      <c r="E112" s="6">
+      <c r="E112" s="8">
         <v>5.7639999999999993</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="8"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A114" s="2" t="s">
-        <v>222</v>
+      <c r="A114" s="7" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="B115" s="1">
         <v>20.646079347779501</v>
@@ -3709,7 +3522,7 @@
       <c r="D115" s="1">
         <v>46.98414205369383</v>
       </c>
-      <c r="E115" s="1">
+      <c r="E115" s="7">
         <v>6.0840000000000005</v>
       </c>
       <c r="F115" s="1"/>
@@ -3719,7 +3532,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="B116" s="1">
         <v>20.484073948782164</v>
@@ -3730,14 +3543,14 @@
       <c r="D116" s="1">
         <v>47.025010182305351</v>
       </c>
-      <c r="E116" s="1">
+      <c r="E116" s="7">
         <v>7.5569999999999995</v>
       </c>
       <c r="F116" s="1"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="B117" s="1">
         <v>22.167656181063784</v>
@@ -3748,14 +3561,14 @@
       <c r="D117" s="1">
         <v>44.722222681223244</v>
       </c>
-      <c r="E117" s="1">
+      <c r="E117" s="7">
         <v>2.2109999999999999</v>
       </c>
       <c r="F117" s="1"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="B118" s="1">
         <v>20.484631267287387</v>
@@ -3766,14 +3579,14 @@
       <c r="D118" s="1">
         <v>45.782071759710149</v>
       </c>
-      <c r="E118" s="1">
+      <c r="E118" s="7">
         <v>3.9250000000000007</v>
       </c>
       <c r="F118" s="1"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="B119" s="1">
         <v>20.974789912325281</v>
@@ -3784,13 +3597,13 @@
       <c r="D119" s="1">
         <v>49.753175448212232</v>
       </c>
-      <c r="E119" s="1">
+      <c r="E119" s="7">
         <v>15.530000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="B120" s="1">
         <v>20.85162987917419</v>
@@ -3801,13 +3614,13 @@
       <c r="D120" s="1">
         <v>47.276516269059854</v>
       </c>
-      <c r="E120" s="1">
+      <c r="E120" s="7">
         <v>5.29</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="B121" s="1">
         <v>20.280207180422028</v>
@@ -3818,13 +3631,13 @@
       <c r="D121" s="1">
         <v>46.70800870967976</v>
       </c>
-      <c r="E121" s="1">
+      <c r="E121" s="7">
         <v>8.0830000000000002</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="B122" s="1">
         <v>21.694023743641949</v>
@@ -3835,13 +3648,13 @@
       <c r="D122" s="1">
         <v>50.150906072402208</v>
       </c>
-      <c r="E122" s="1">
+      <c r="E122" s="7">
         <v>20.887</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="B123" s="1">
         <v>20.802331306643765</v>
@@ -3852,13 +3665,13 @@
       <c r="D123" s="1">
         <v>46.552386378599252</v>
       </c>
-      <c r="E123" s="1">
+      <c r="E123" s="7">
         <v>3.5809999999999995</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="B124" s="1">
         <v>21.573040122399583</v>
@@ -3869,7 +3682,7 @@
       <c r="D124" s="1">
         <v>47.301557397638788</v>
       </c>
-      <c r="E124" s="1">
+      <c r="E124" s="7">
         <v>2.6469999999999998</v>
       </c>
     </row>
@@ -3877,20 +3690,18 @@
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A126" s="2" t="s">
-        <v>114</v>
+      <c r="A126" s="7" t="s">
+        <v>173</v>
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="B127" s="1">
         <v>20.764639984442496</v>
@@ -3901,7 +3712,7 @@
       <c r="D127" s="1">
         <v>46.702029647528732</v>
       </c>
-      <c r="E127" s="1">
+      <c r="E127" s="7">
         <v>4.8249999999999993</v>
       </c>
       <c r="F127" s="1"/>
@@ -3911,7 +3722,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="B128" s="1">
         <v>21.617328784710757</v>
@@ -3922,14 +3733,14 @@
       <c r="D128" s="1">
         <v>48.102710832324561</v>
       </c>
-      <c r="E128" s="1">
+      <c r="E128" s="7">
         <v>5.9539999999999997</v>
       </c>
       <c r="F128" s="1"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="B129" s="1">
         <v>20.686868583346357</v>
@@ -3940,14 +3751,14 @@
       <c r="D129" s="1">
         <v>44.166254583095267</v>
       </c>
-      <c r="E129" s="1">
+      <c r="E129" s="7">
         <v>2.7940000000000005</v>
       </c>
       <c r="F129" s="1"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="B130" s="1">
         <v>20.448953465849936</v>
@@ -3958,14 +3769,14 @@
       <c r="D130" s="1">
         <v>45.633489092801973</v>
       </c>
-      <c r="E130" s="1">
+      <c r="E130" s="7">
         <v>3.653</v>
       </c>
       <c r="F130" s="1"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="B131" s="1">
         <v>22.350278836483788</v>
@@ -3976,13 +3787,13 @@
       <c r="D131" s="1">
         <v>49.999569684710337</v>
       </c>
-      <c r="E131" s="1">
+      <c r="E131" s="7">
         <v>5.0560000000000009</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="B132" s="1">
         <v>20.045790554414779</v>
@@ -3993,13 +3804,13 @@
       <c r="D132" s="1">
         <v>46.288618363156345</v>
       </c>
-      <c r="E132" s="1">
+      <c r="E132" s="7">
         <v>6.9090000000000007</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="B133" s="1">
         <v>20.644499570651654</v>
@@ -4010,13 +3821,13 @@
       <c r="D133" s="1">
         <v>48.221421343885424</v>
       </c>
-      <c r="E133" s="1">
+      <c r="E133" s="7">
         <v>7.1400000000000006</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="B134" s="1">
         <v>19.271132768965842</v>
@@ -4027,13 +3838,13 @@
       <c r="D134" s="1">
         <v>47.648614330323959</v>
       </c>
-      <c r="E134" s="1">
+      <c r="E134" s="7">
         <v>14.311</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="B135" s="1">
         <v>19.626997250077046</v>
@@ -4044,13 +3855,13 @@
       <c r="D135" s="1">
         <v>45.987705355237892</v>
       </c>
-      <c r="E135" s="1">
+      <c r="E135" s="7">
         <v>3.6789999999999998</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="B136" s="1">
         <v>19.611511388966846</v>
@@ -4061,18 +3872,18 @@
       <c r="D136" s="1">
         <v>45.764662427861275</v>
       </c>
-      <c r="E136" s="1">
+      <c r="E136" s="7">
         <v>3.1509999999999998</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A138" s="2" t="s">
-        <v>115</v>
+      <c r="A138" s="7" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
       <c r="B139" s="1">
         <v>19.007042011169681</v>
@@ -4083,7 +3894,7 @@
       <c r="D139" s="1">
         <v>44.615970809430841</v>
       </c>
-      <c r="E139" s="2">
+      <c r="E139" s="7">
         <v>6.1660000000000004</v>
       </c>
       <c r="G139" s="1"/>
@@ -4092,7 +3903,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="B140" s="1">
         <v>21.47405597048575</v>
@@ -4103,14 +3914,14 @@
       <c r="D140" s="1">
         <v>46.065040687477008</v>
       </c>
-      <c r="E140" s="2">
+      <c r="E140" s="7">
         <v>3.9769999999999999</v>
       </c>
       <c r="F140" s="1"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
-        <v>118</v>
+        <v>177</v>
       </c>
       <c r="B141" s="1">
         <v>20.055111035922067</v>
@@ -4121,14 +3932,14 @@
       <c r="D141" s="1">
         <v>49.071163603613243</v>
       </c>
-      <c r="E141" s="2">
+      <c r="E141" s="7">
         <v>15.97</v>
       </c>
       <c r="F141" s="1"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A142" s="2" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="B142" s="1">
         <v>20.582617891080979</v>
@@ -4139,14 +3950,14 @@
       <c r="D142" s="1">
         <v>49.896217089969127</v>
       </c>
-      <c r="E142" s="2">
+      <c r="E142" s="7">
         <v>19.588999999999999</v>
       </c>
       <c r="F142" s="1"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B143" s="1">
         <v>20.191187777442291</v>
@@ -4157,13 +3968,13 @@
       <c r="D143" s="1">
         <v>49.290912881191389</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="7">
         <v>12.134</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="B144" s="1">
         <v>19.821637583335466</v>
@@ -4174,13 +3985,13 @@
       <c r="D144" s="1">
         <v>47.758860955572935</v>
       </c>
-      <c r="E144" s="2">
+      <c r="E144" s="7">
         <v>16.798999999999999</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="B145" s="1">
         <v>20.570377091005383</v>
@@ -4191,13 +4002,13 @@
       <c r="D145" s="1">
         <v>47.739217967606578</v>
       </c>
-      <c r="E145" s="2">
+      <c r="E145" s="7">
         <v>7.7439999999999998</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
-        <v>123</v>
+        <v>182</v>
       </c>
       <c r="B146" s="1">
         <v>21.532580754815072</v>
@@ -4208,13 +4019,13 @@
       <c r="D146" s="1">
         <v>44.484077876546614</v>
       </c>
-      <c r="E146" s="2">
+      <c r="E146" s="7">
         <v>2.6840000000000002</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
-        <v>124</v>
+        <v>183</v>
       </c>
       <c r="B147" s="1">
         <v>19.53130242526165</v>
@@ -4225,13 +4036,13 @@
       <c r="D147" s="1">
         <v>46.515365916444317</v>
       </c>
-      <c r="E147" s="2">
+      <c r="E147" s="7">
         <v>8.8309999999999995</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
       <c r="B148" s="1">
         <v>19.481711327878354</v>
@@ -4242,18 +4053,18 @@
       <c r="D148" s="1">
         <v>46.154985925875266</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="7">
         <v>6.6180000000000003</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A150" s="8" t="s">
-        <v>136</v>
+      <c r="A150" s="7" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="B151" s="1">
         <v>21.152353097103408</v>
@@ -4264,7 +4075,7 @@
       <c r="D151" s="1">
         <v>43.605506220759246</v>
       </c>
-      <c r="E151" s="1">
+      <c r="E151" s="7">
         <v>3</v>
       </c>
       <c r="F151" s="1"/>
@@ -4274,7 +4085,7 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="B152" s="1">
         <v>20.966685863946136</v>
@@ -4285,14 +4096,14 @@
       <c r="D152" s="1">
         <v>44.410934907510246</v>
       </c>
-      <c r="E152" s="1">
+      <c r="E152" s="7">
         <v>3.75</v>
       </c>
       <c r="F152" s="1"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="B153" s="1">
         <v>19.591044576552466</v>
@@ -4303,14 +4114,14 @@
       <c r="D153" s="1">
         <v>45.855964504712318</v>
       </c>
-      <c r="E153" s="1">
+      <c r="E153" s="7">
         <v>7.6259999999999994</v>
       </c>
       <c r="F153" s="1"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="B154" s="1">
         <v>19.850451359080839</v>
@@ -4321,14 +4132,14 @@
       <c r="D154" s="1">
         <v>47.803159110977511</v>
       </c>
-      <c r="E154" s="1">
+      <c r="E154" s="7">
         <v>12.926</v>
       </c>
       <c r="F154" s="1"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="B155" s="1">
         <v>20.212726616860682</v>
@@ -4339,13 +4150,13 @@
       <c r="D155" s="1">
         <v>49.342665842868897</v>
       </c>
-      <c r="E155" s="1">
+      <c r="E155" s="7">
         <v>12.637</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="B156" s="1">
         <v>21.460233687984605</v>
@@ -4356,13 +4167,13 @@
       <c r="D156" s="1">
         <v>49.631263883148208</v>
       </c>
-      <c r="E156" s="1">
+      <c r="E156" s="7">
         <v>7.3080000000000007</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="B157" s="1">
         <v>25.44600332036034</v>
@@ -4373,13 +4184,13 @@
       <c r="D157" s="1">
         <v>43.421536074898626</v>
       </c>
-      <c r="E157" s="1">
+      <c r="E157" s="7">
         <v>1.536</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="B158" s="1">
         <v>19.548230267142184</v>
@@ -4390,13 +4201,13 @@
       <c r="D158" s="1">
         <v>46.891929867708214</v>
       </c>
-      <c r="E158" s="1">
+      <c r="E158" s="7">
         <v>12.697000000000001</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
-        <v>145</v>
+        <v>194</v>
       </c>
       <c r="B159" s="1">
         <v>19.785397016279077</v>
@@ -4407,13 +4218,13 @@
       <c r="D159" s="1">
         <v>46.003690679364396</v>
       </c>
-      <c r="E159" s="1">
+      <c r="E159" s="7">
         <v>6.286999999999999</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="B160" s="1">
         <v>20.948772998004536</v>
@@ -4424,18 +4235,18 @@
       <c r="D160" s="1">
         <v>45.127490070011625</v>
       </c>
-      <c r="E160" s="1">
+      <c r="E160" s="7">
         <v>3.5609999999999999</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A162" s="3" t="s">
-        <v>213</v>
+      <c r="A162" s="7" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="B163" s="1">
         <v>20.665830148189123</v>
@@ -4446,14 +4257,14 @@
       <c r="D163" s="1">
         <v>45.409030163123035</v>
       </c>
-      <c r="E163" s="1">
+      <c r="E163" s="7">
         <v>6.4359999999999999</v>
       </c>
       <c r="F163" s="1"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="B164" s="1">
         <v>21.913040756577683</v>
@@ -4464,14 +4275,14 @@
       <c r="D164" s="1">
         <v>45.383417119303516</v>
       </c>
-      <c r="E164" s="1">
+      <c r="E164" s="7">
         <v>2.8869999999999996</v>
       </c>
       <c r="F164" s="1"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="B165" s="1">
         <v>20.628338712905332</v>
@@ -4482,14 +4293,14 @@
       <c r="D165" s="1">
         <v>49.051502452879568</v>
       </c>
-      <c r="E165" s="1">
+      <c r="E165" s="7">
         <v>15.794</v>
       </c>
       <c r="F165" s="1"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="B166" s="1">
         <v>20.700052448422529</v>
@@ -4500,14 +4311,14 @@
       <c r="D166" s="1">
         <v>45.86493956946353</v>
       </c>
-      <c r="E166" s="1">
+      <c r="E166" s="7">
         <v>5.5989999999999993</v>
       </c>
       <c r="F166" s="1"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="B167" s="1">
         <v>20.305909208537106</v>
@@ -4518,13 +4329,13 @@
       <c r="D167" s="1">
         <v>48.659825846043063</v>
       </c>
-      <c r="E167" s="1">
+      <c r="E167" s="7">
         <v>14.95</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="B168" s="1">
         <v>20.621226893270691</v>
@@ -4535,13 +4346,13 @@
       <c r="D168" s="1">
         <v>48.088298783252512</v>
       </c>
-      <c r="E168" s="1">
+      <c r="E168" s="7">
         <v>10.882</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
-        <v>153</v>
+        <v>203</v>
       </c>
       <c r="B169" s="1">
         <v>24.184490973784172</v>
@@ -4552,13 +4363,13 @@
       <c r="D169" s="1">
         <v>46.99686011321181</v>
       </c>
-      <c r="E169" s="1">
+      <c r="E169" s="7">
         <v>2.8039999999999998</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
-        <v>154</v>
+        <v>204</v>
       </c>
       <c r="B170" s="1">
         <v>21.919725495507702</v>
@@ -4569,13 +4380,13 @@
       <c r="D170" s="1">
         <v>49.358464264752364</v>
       </c>
-      <c r="E170" s="1">
+      <c r="E170" s="7">
         <v>3.3679999999999994</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="B171" s="1">
         <v>19.819858660384909</v>
@@ -4586,13 +4397,13 @@
       <c r="D171" s="1">
         <v>46.484762285731215</v>
       </c>
-      <c r="E171" s="1">
+      <c r="E171" s="7">
         <v>7.3509999999999991</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="B172" s="1">
         <v>21.576813674300887</v>
@@ -4603,7 +4414,7 @@
       <c r="D172" s="1">
         <v>45.788532235462881</v>
       </c>
-      <c r="E172" s="1">
+      <c r="E172" s="7">
         <v>4.5090000000000003</v>
       </c>
     </row>
@@ -4611,16 +4422,15 @@
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
-      <c r="E173" s="1"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A174" s="8" t="s">
-        <v>214</v>
+      <c r="A174" s="7" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A175" s="2" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="B175" s="1">
         <v>20.258117409259441</v>
@@ -4631,32 +4441,32 @@
       <c r="D175" s="1">
         <v>48.580800852652828</v>
       </c>
-      <c r="E175" s="1">
+      <c r="E175" s="7">
         <v>14.343999999999999</v>
       </c>
       <c r="F175" s="1"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A176" s="2" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="B176" s="1">
-        <v>20.152585321431811</v>
+        <v>20.278525866771922</v>
       </c>
       <c r="C176" s="1">
-        <v>32.035440779326393</v>
+        <v>31.610635131809214</v>
       </c>
       <c r="D176" s="1">
-        <v>47.811973899241792</v>
-      </c>
-      <c r="E176" s="1">
-        <v>13.094000000000001</v>
+        <v>48.11083900141886</v>
+      </c>
+      <c r="E176" s="7">
+        <v>13.01</v>
       </c>
       <c r="F176" s="1"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="B177" s="1">
         <v>20.775868513579347</v>
@@ -4667,14 +4477,14 @@
       <c r="D177" s="1">
         <v>46.116768835277838</v>
       </c>
-      <c r="E177" s="1">
+      <c r="E177" s="7">
         <v>6.3099999999999987</v>
       </c>
       <c r="F177" s="1"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A178" s="2" t="s">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="B178" s="1">
         <v>21.371398426011364</v>
@@ -4685,14 +4495,14 @@
       <c r="D178" s="1">
         <v>46.509826334852846</v>
       </c>
-      <c r="E178" s="1">
+      <c r="E178" s="7">
         <v>5.6009999999999991</v>
       </c>
       <c r="F178" s="1"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A179" s="2" t="s">
-        <v>161</v>
+        <v>212</v>
       </c>
       <c r="B179" s="1">
         <v>20.428770757139048</v>
@@ -4703,13 +4513,13 @@
       <c r="D179" s="1">
         <v>49.888722606299794</v>
       </c>
-      <c r="E179" s="1">
+      <c r="E179" s="7">
         <v>18.303999999999998</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A180" s="2" t="s">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="B180" s="1">
         <v>19.927784502378216</v>
@@ -4720,13 +4530,13 @@
       <c r="D180" s="1">
         <v>46.963322212575974</v>
       </c>
-      <c r="E180" s="1">
+      <c r="E180" s="7">
         <v>8.3150000000000013</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A181" s="2" t="s">
-        <v>163</v>
+        <v>214</v>
       </c>
       <c r="B181" s="1">
         <v>19.875765649684755</v>
@@ -4737,13 +4547,13 @@
       <c r="D181" s="1">
         <v>47.44149192134504</v>
       </c>
-      <c r="E181" s="1">
+      <c r="E181" s="7">
         <v>10.689</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A182" s="2" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="B182" s="1">
         <v>20.93552299165454</v>
@@ -4754,13 +4564,13 @@
       <c r="D182" s="1">
         <v>49.368812304837434</v>
       </c>
-      <c r="E182" s="1">
+      <c r="E182" s="7">
         <v>17.494</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A183" s="2" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="B183" s="1">
         <v>24.814016195989772</v>
@@ -4771,13 +4581,13 @@
       <c r="D183" s="1">
         <v>45.512212333869137</v>
       </c>
-      <c r="E183" s="1">
+      <c r="E183" s="7">
         <v>2.1440000000000001</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A184" s="2" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="B184" s="1">
         <v>20.895757152149013</v>
@@ -4788,7 +4598,7 @@
       <c r="D184" s="1">
         <v>45.082214343389296</v>
       </c>
-      <c r="E184" s="1">
+      <c r="E184" s="7">
         <v>4.7080000000000002</v>
       </c>
     </row>
@@ -4796,16 +4606,15 @@
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
-      <c r="E185" s="1"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A186" s="2" t="s">
-        <v>223</v>
+      <c r="A186" s="7" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A187" s="2" t="s">
-        <v>167</v>
+        <v>42</v>
       </c>
       <c r="B187" s="1">
         <v>22.050023994297316</v>
@@ -4816,14 +4625,14 @@
       <c r="D187" s="1">
         <v>50.560843955621749</v>
       </c>
-      <c r="E187" s="1">
+      <c r="E187" s="7">
         <v>25.423999999999999</v>
       </c>
       <c r="F187" s="1"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A188" s="2" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="B188" s="1">
         <v>22.019633909397687</v>
@@ -4834,14 +4643,14 @@
       <c r="D188" s="1">
         <v>48.661672972696593</v>
       </c>
-      <c r="E188" s="1">
+      <c r="E188" s="7">
         <v>18.384</v>
       </c>
       <c r="F188" s="1"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A189" s="2" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
       <c r="B189" s="1">
         <v>21.26696925453102</v>
@@ -4852,14 +4661,14 @@
       <c r="D189" s="1">
         <v>49.46914499784684</v>
       </c>
-      <c r="E189" s="1">
+      <c r="E189" s="7">
         <v>20.134</v>
       </c>
       <c r="F189" s="1"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A190" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="B190" s="1">
         <v>21.33636418906595</v>
@@ -4870,31 +4679,31 @@
       <c r="D190" s="1">
         <v>50.537393689244965</v>
       </c>
-      <c r="E190" s="1">
+      <c r="E190" s="7">
         <v>17.22</v>
       </c>
       <c r="F190" s="1"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A191" s="2" t="s">
-        <v>171</v>
+        <v>46</v>
       </c>
       <c r="B191" s="1">
-        <v>19.163597876500425</v>
+        <v>18.866889426347321</v>
       </c>
       <c r="C191" s="1">
-        <v>34.174596299656351</v>
+        <v>34.68578424545872</v>
       </c>
       <c r="D191" s="1">
-        <v>46.661805823843217</v>
-      </c>
-      <c r="E191" s="1">
-        <v>10.88</v>
+        <v>46.447326328193959</v>
+      </c>
+      <c r="E191" s="7">
+        <v>11.646000000000001</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A192" s="2" t="s">
-        <v>172</v>
+        <v>47</v>
       </c>
       <c r="B192" s="1">
         <v>19.640548534984269</v>
@@ -4905,13 +4714,13 @@
       <c r="D192" s="1">
         <v>47.054559645180575</v>
       </c>
-      <c r="E192" s="1">
+      <c r="E192" s="7">
         <v>10.936</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A193" s="2" t="s">
-        <v>173</v>
+        <v>48</v>
       </c>
       <c r="B193" s="1">
         <v>21.904549828450961</v>
@@ -4922,13 +4731,13 @@
       <c r="D193" s="1">
         <v>50.228792453214353</v>
       </c>
-      <c r="E193" s="1">
+      <c r="E193" s="7">
         <v>24.049999999999997</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A194" s="2" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="B194" s="1">
         <v>21.613084366120802</v>
@@ -4939,41 +4748,40 @@
       <c r="D194" s="1">
         <v>50.071003512299058</v>
       </c>
-      <c r="E194" s="1">
+      <c r="E194" s="7">
         <v>13.155999999999999</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A195" s="2" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="B195" s="1">
-        <v>20.789945318144241</v>
+        <v>18.101070547992649</v>
       </c>
       <c r="C195" s="1">
-        <v>29.613470972368642</v>
+        <v>36.620465142098638</v>
       </c>
       <c r="D195" s="1">
-        <v>49.596583709487128</v>
-      </c>
-      <c r="E195" s="1">
-        <v>19.384</v>
+        <v>45.278464309908713</v>
+      </c>
+      <c r="E195" s="7">
+        <v>11.414000000000001</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
-      <c r="E196" s="1"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A197" s="8" t="s">
-        <v>224</v>
+      <c r="A197" s="7" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A198" s="2" t="s">
-        <v>176</v>
+        <v>50</v>
       </c>
       <c r="B198" s="1">
         <v>20.73405627831108</v>
@@ -4984,14 +4792,14 @@
       <c r="D198" s="1">
         <v>48.10134585983279</v>
       </c>
-      <c r="E198" s="1">
+      <c r="E198" s="7">
         <v>9.1939999999999991</v>
       </c>
       <c r="F198" s="1"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A199" s="2" t="s">
-        <v>177</v>
+        <v>51</v>
       </c>
       <c r="B199" s="1">
         <v>21.075968236006723</v>
@@ -5002,13 +4810,13 @@
       <c r="D199" s="1">
         <v>48.583231023898115</v>
       </c>
-      <c r="E199" s="1">
+      <c r="E199" s="7">
         <v>12.340999999999999</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A200" s="2" t="s">
-        <v>178</v>
+        <v>52</v>
       </c>
       <c r="B200" s="1">
         <v>21.671009661875708</v>
@@ -5019,13 +4827,13 @@
       <c r="D200" s="1">
         <v>47.635258288342044</v>
       </c>
-      <c r="E200" s="1">
+      <c r="E200" s="7">
         <v>8.1709999999999994</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A201" s="2" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="B201" s="1">
         <v>19.754927019660261</v>
@@ -5036,13 +4844,13 @@
       <c r="D201" s="1">
         <v>46.832727322161915</v>
       </c>
-      <c r="E201" s="1">
+      <c r="E201" s="7">
         <v>10.119</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A202" s="2" t="s">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="B202" s="1">
         <v>19.423500858088651</v>
@@ -5053,13 +4861,13 @@
       <c r="D202" s="1">
         <v>46.170225879570786</v>
       </c>
-      <c r="E202" s="1">
+      <c r="E202" s="7">
         <v>8.9580000000000002</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A203" s="2" t="s">
-        <v>181</v>
+        <v>55</v>
       </c>
       <c r="B203" s="1">
         <v>19.534670693537553</v>
@@ -5070,13 +4878,13 @@
       <c r="D203" s="1">
         <v>46.706753717988661</v>
       </c>
-      <c r="E203" s="1">
+      <c r="E203" s="7">
         <v>10.175999999999998</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A204" s="2" t="s">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="B204" s="1">
         <v>19.492052352769711</v>
@@ -5087,13 +4895,13 @@
       <c r="D204" s="1">
         <v>46.250782453666062</v>
       </c>
-      <c r="E204" s="1">
+      <c r="E204" s="7">
         <v>8.4090000000000007</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A205" s="2" t="s">
-        <v>183</v>
+        <v>57</v>
       </c>
       <c r="B205" s="1">
         <v>20.019961746428606</v>
@@ -5104,13 +4912,13 @@
       <c r="D205" s="1">
         <v>46.506964964119888</v>
       </c>
-      <c r="E205" s="1">
+      <c r="E205" s="7">
         <v>8.5120000000000005</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A206" s="2" t="s">
-        <v>184</v>
+        <v>58</v>
       </c>
       <c r="B206" s="1">
         <v>19.482835597985606</v>
@@ -5121,13 +4929,13 @@
       <c r="D206" s="1">
         <v>46.653255708277186</v>
       </c>
-      <c r="E206" s="1">
+      <c r="E206" s="7">
         <v>7.43</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A207" s="2" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="B207" s="1">
         <v>19.70069153951556</v>
@@ -5138,7 +4946,7 @@
       <c r="D207" s="1">
         <v>45.137546381830518</v>
       </c>
-      <c r="E207" s="1">
+      <c r="E207" s="7">
         <v>6.8769999999999998</v>
       </c>
     </row>
@@ -5146,20 +4954,18 @@
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
-      <c r="E208" s="1"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A209" s="8" t="s">
-        <v>225</v>
+      <c r="A209" s="7" t="s">
+        <v>220</v>
       </c>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
-      <c r="E209" s="1"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A210" s="2" t="s">
-        <v>186</v>
+        <v>60</v>
       </c>
       <c r="B210" s="1">
         <v>19.526355608584751</v>
@@ -5170,14 +4976,14 @@
       <c r="D210" s="1">
         <v>46.669947689401539</v>
       </c>
-      <c r="E210" s="1">
+      <c r="E210" s="7">
         <v>13.288999999999998</v>
       </c>
       <c r="F210" s="1"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A211" s="2" t="s">
-        <v>187</v>
+        <v>61</v>
       </c>
       <c r="B211" s="1">
         <v>20.848502859699586</v>
@@ -5188,13 +4994,13 @@
       <c r="D211" s="1">
         <v>49.441916736373813</v>
       </c>
-      <c r="E211" s="1">
+      <c r="E211" s="7">
         <v>18.812000000000001</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A212" s="2" t="s">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="B212" s="1">
         <v>19.474283661831755</v>
@@ -5205,13 +5011,13 @@
       <c r="D212" s="1">
         <v>47.116635178149224</v>
       </c>
-      <c r="E212" s="1">
+      <c r="E212" s="7">
         <v>16.457999999999998</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A213" s="2" t="s">
-        <v>189</v>
+        <v>63</v>
       </c>
       <c r="B213" s="1">
         <v>19.139297293650973</v>
@@ -5222,13 +5028,13 @@
       <c r="D213" s="1">
         <v>45.293874522337518</v>
       </c>
-      <c r="E213" s="1">
+      <c r="E213" s="7">
         <v>5.7160000000000002</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A214" s="2" t="s">
-        <v>190</v>
+        <v>64</v>
       </c>
       <c r="B214" s="1">
         <v>20.477552945607105</v>
@@ -5239,13 +5045,13 @@
       <c r="D214" s="1">
         <v>48.507559296648679</v>
       </c>
-      <c r="E214" s="1">
+      <c r="E214" s="7">
         <v>14.907999999999999</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A215" s="2" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B215" s="1">
         <v>19.267578841123505</v>
@@ -5256,13 +5062,13 @@
       <c r="D215" s="1">
         <v>46.186836803804837</v>
       </c>
-      <c r="E215" s="1">
+      <c r="E215" s="7">
         <v>11.853999999999999</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A216" s="2" t="s">
-        <v>192</v>
+        <v>66</v>
       </c>
       <c r="B216" s="1">
         <v>19.314702550102872</v>
@@ -5273,13 +5079,13 @@
       <c r="D216" s="1">
         <v>42.724026754654076</v>
       </c>
-      <c r="E216" s="1">
+      <c r="E216" s="7">
         <v>3.0029999999999997</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A217" s="2" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="B217" s="1">
         <v>20.937161990549246</v>
@@ -5290,13 +5096,13 @@
       <c r="D217" s="1">
         <v>49.314557553905388</v>
       </c>
-      <c r="E217" s="1">
+      <c r="E217" s="7">
         <v>21.985999999999997</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A218" s="2" t="s">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="B218" s="1">
         <v>20.178659064761899</v>
@@ -5307,13 +5113,13 @@
       <c r="D218" s="1">
         <v>47.42752258872811</v>
       </c>
-      <c r="E218" s="1">
+      <c r="E218" s="7">
         <v>10.083000000000002</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A219" s="2" t="s">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="B219" s="1">
         <v>20.316794904026068</v>
@@ -5324,7 +5130,7 @@
       <c r="D219" s="1">
         <v>48.235822149285354</v>
       </c>
-      <c r="E219" s="1">
+      <c r="E219" s="7">
         <v>16.612000000000002</v>
       </c>
     </row>
@@ -5332,20 +5138,18 @@
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
-      <c r="E220" s="1"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A221" s="8" t="s">
-        <v>226</v>
+      <c r="A221" s="7" t="s">
+        <v>221</v>
       </c>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
-      <c r="E221" s="1"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A222" s="2" t="s">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="B222" s="1">
         <v>18.663139082750192</v>
@@ -5356,14 +5160,14 @@
       <c r="D222" s="1">
         <v>46.815154612648648</v>
       </c>
-      <c r="E222" s="1">
+      <c r="E222" s="7">
         <v>12.731000000000002</v>
       </c>
       <c r="F222" s="1"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A223" s="2" t="s">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="B223" s="1">
         <v>20.865425556262181</v>
@@ -5374,13 +5178,13 @@
       <c r="D223" s="1">
         <v>49.049578811347715</v>
       </c>
-      <c r="E223" s="1">
+      <c r="E223" s="7">
         <v>22.14</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A224" s="2" t="s">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="B224" s="1">
         <v>20.22263070936182</v>
@@ -5391,13 +5195,13 @@
       <c r="D224" s="1">
         <v>48.189489294015459</v>
       </c>
-      <c r="E224" s="1">
+      <c r="E224" s="7">
         <v>19.588999999999999</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A225" s="2" t="s">
-        <v>199</v>
+        <v>73</v>
       </c>
       <c r="B225" s="1">
         <v>19.17804721411936</v>
@@ -5408,13 +5212,13 @@
       <c r="D225" s="1">
         <v>47.643691501406934</v>
       </c>
-      <c r="E225" s="1">
+      <c r="E225" s="7">
         <v>13.645999999999999</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A226" s="2" t="s">
-        <v>200</v>
+        <v>74</v>
       </c>
       <c r="B226" s="1">
         <v>19.327588477264896</v>
@@ -5425,13 +5229,13 @@
       <c r="D226" s="1">
         <v>48.01596926438814</v>
       </c>
-      <c r="E226" s="1">
+      <c r="E226" s="7">
         <v>16.005000000000003</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A227" s="2" t="s">
-        <v>201</v>
+        <v>75</v>
       </c>
       <c r="B227" s="1">
         <v>20.436994312767602</v>
@@ -5442,13 +5246,13 @@
       <c r="D227" s="1">
         <v>49.184300038521911</v>
       </c>
-      <c r="E227" s="1">
+      <c r="E227" s="7">
         <v>16.064</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A228" s="2" t="s">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="B228" s="1">
         <v>19.218117868036927</v>
@@ -5459,13 +5263,13 @@
       <c r="D228" s="1">
         <v>48.060702990585384</v>
       </c>
-      <c r="E228" s="1">
+      <c r="E228" s="7">
         <v>19.294</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A229" s="2" t="s">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="B229" s="1">
         <v>19.472164184607458</v>
@@ -5476,7 +5280,7 @@
       <c r="D229" s="1">
         <v>47.743394117066885</v>
       </c>
-      <c r="E229" s="1">
+      <c r="E229" s="7">
         <v>16.899000000000001</v>
       </c>
     </row>
@@ -5484,20 +5288,18 @@
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
-      <c r="E230" s="1"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A231" s="8" t="s">
-        <v>227</v>
+      <c r="A231" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
-      <c r="E231" s="1"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A232" s="2" t="s">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="B232" s="1">
         <v>19.292844885323383</v>
@@ -5508,14 +5310,14 @@
       <c r="D232" s="1">
         <v>47.286929907170723</v>
       </c>
-      <c r="E232" s="1">
+      <c r="E232" s="7">
         <v>14.793000000000001</v>
       </c>
       <c r="F232" s="1"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A233" s="2" t="s">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="B233" s="1">
         <v>19.286450555855787</v>
@@ -5526,13 +5328,13 @@
       <c r="D233" s="1">
         <v>47.834013822880863</v>
       </c>
-      <c r="E233" s="1">
+      <c r="E233" s="7">
         <v>16.475999999999999</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A234" s="2" t="s">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="B234" s="1">
         <v>19.204530498237816</v>
@@ -5543,13 +5345,13 @@
       <c r="D234" s="1">
         <v>47.705259258176014</v>
       </c>
-      <c r="E234" s="1">
+      <c r="E234" s="7">
         <v>13.679999999999998</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A235" s="2" t="s">
-        <v>207</v>
+        <v>81</v>
       </c>
       <c r="B235" s="1">
         <v>19.595171006857349</v>
@@ -5560,13 +5362,13 @@
       <c r="D235" s="1">
         <v>48.105544975575</v>
       </c>
-      <c r="E235" s="1">
+      <c r="E235" s="7">
         <v>16.152000000000001</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A236" s="2" t="s">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="B236" s="1">
         <v>20.247937332263401</v>
@@ -5577,13 +5379,13 @@
       <c r="D236" s="1">
         <v>48.758819955212061</v>
       </c>
-      <c r="E236" s="1">
+      <c r="E236" s="7">
         <v>16.474</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A237" s="2" t="s">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="B237" s="1">
         <v>19.634102178920845</v>
@@ -5594,13 +5396,13 @@
       <c r="D237" s="1">
         <v>49.846995606639183</v>
       </c>
-      <c r="E237" s="1">
+      <c r="E237" s="7">
         <v>21.577999999999999</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A238" s="2" t="s">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="B238" s="1">
         <v>19.190419704186088</v>
@@ -5611,13 +5413,13 @@
       <c r="D238" s="1">
         <v>47.438579187659322</v>
       </c>
-      <c r="E238" s="1">
+      <c r="E238" s="7">
         <v>14.836</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A239" s="2" t="s">
-        <v>211</v>
+        <v>85</v>
       </c>
       <c r="B239" s="1">
         <v>17.53476568584199</v>
@@ -5628,13 +5430,13 @@
       <c r="D239" s="1">
         <v>46.028153416712804</v>
       </c>
-      <c r="E239" s="1">
+      <c r="E239" s="7">
         <v>8.8719999999999999</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A240" s="2" t="s">
-        <v>212</v>
+        <v>86</v>
       </c>
       <c r="B240" s="1">
         <v>19.468944456145053</v>
@@ -5645,7 +5447,7 @@
       <c r="D240" s="1">
         <v>48.035742595110001</v>
       </c>
-      <c r="E240" s="1">
+      <c r="E240" s="7">
         <v>14.453999999999999</v>
       </c>
     </row>
@@ -5653,16 +5455,15 @@
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
-      <c r="E241" s="1"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A242" s="8" t="s">
-        <v>228</v>
+      <c r="A242" s="7" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A243" s="2" t="s">
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="B243" s="1">
         <v>21.972140875471396</v>
@@ -5673,14 +5474,14 @@
       <c r="D243" s="1">
         <v>49.877741263538013</v>
       </c>
-      <c r="E243" s="1">
+      <c r="E243" s="7">
         <v>26.173999999999999</v>
       </c>
       <c r="F243" s="1"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A244" s="2" t="s">
-        <v>230</v>
+        <v>88</v>
       </c>
       <c r="B244" s="1">
         <v>22.136781490597532</v>
@@ -5691,13 +5492,13 @@
       <c r="D244" s="1">
         <v>50.588988110696022</v>
       </c>
-      <c r="E244" s="1">
+      <c r="E244" s="7">
         <v>16.606999999999999</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A245" s="2" t="s">
-        <v>231</v>
+        <v>89</v>
       </c>
       <c r="B245" s="1">
         <v>20.769340943937152</v>
@@ -5708,13 +5509,13 @@
       <c r="D245" s="1">
         <v>49.72814477859125</v>
       </c>
-      <c r="E245" s="1">
+      <c r="E245" s="7">
         <v>22.494</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A246" s="2" t="s">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="B246" s="1">
         <v>20.46377713324943</v>
@@ -5725,13 +5526,13 @@
       <c r="D246" s="1">
         <v>48.92109003029006</v>
       </c>
-      <c r="E246" s="1">
+      <c r="E246" s="7">
         <v>12.559000000000001</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A247" s="2" t="s">
-        <v>233</v>
+        <v>91</v>
       </c>
       <c r="B247" s="1">
         <v>20.43087323187671</v>
@@ -5742,421 +5543,402 @@
       <c r="D247" s="1">
         <v>49.371711036674157</v>
       </c>
-      <c r="E247" s="1">
+      <c r="E247" s="7">
         <v>21.689999999999998</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A248" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B248" s="1">
-        <v>20.283946679435019</v>
+        <v>21.015969994927435</v>
       </c>
       <c r="C248" s="1">
-        <v>30.140177304849786</v>
+        <v>26.902989303346146</v>
       </c>
       <c r="D248" s="1">
-        <v>49.575876015715195</v>
-      </c>
-      <c r="E248" s="1">
-        <v>20.338000000000001</v>
+        <v>52.081040701726423</v>
+      </c>
+      <c r="E248" s="7">
+        <v>17.783999999999999</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A249" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B249" s="1">
-        <v>21.015969994927435</v>
+        <v>20.92016534445797</v>
       </c>
       <c r="C249" s="1">
-        <v>26.902989303346146</v>
+        <v>29.610088748293997</v>
       </c>
       <c r="D249" s="1">
-        <v>52.081040701726423</v>
-      </c>
-      <c r="E249" s="1">
-        <v>17.783999999999999</v>
+        <v>49.46974590724804</v>
+      </c>
+      <c r="E249" s="7">
+        <v>23.754999999999999</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A250" s="2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B250" s="1">
-        <v>20.92016534445797</v>
+        <v>22.518403502707816</v>
       </c>
       <c r="C250" s="1">
-        <v>29.610088748293997</v>
+        <v>29.326175794194057</v>
       </c>
       <c r="D250" s="1">
-        <v>49.46974590724804</v>
-      </c>
-      <c r="E250" s="1">
-        <v>23.754999999999999</v>
+        <v>48.15542070309813</v>
+      </c>
+      <c r="E250" s="7">
+        <v>16.032</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A251" s="2" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B251" s="1">
-        <v>22.518403502707816</v>
+        <v>21.648247564886802</v>
       </c>
       <c r="C251" s="1">
-        <v>29.326175794194057</v>
+        <v>28.086012197055346</v>
       </c>
       <c r="D251" s="1">
-        <v>48.15542070309813</v>
-      </c>
-      <c r="E251" s="1">
-        <v>16.032</v>
+        <v>50.265740238057859</v>
+      </c>
+      <c r="E251" s="7">
+        <v>24.883000000000003</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A252" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B252" s="1">
-        <v>21.648247564886802</v>
-      </c>
-      <c r="C252" s="1">
-        <v>28.086012197055346</v>
-      </c>
-      <c r="D252" s="1">
-        <v>50.265740238057859</v>
-      </c>
-      <c r="E252" s="1">
-        <v>24.883000000000003</v>
-      </c>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B253" s="1"/>
-      <c r="C253" s="1"/>
-      <c r="D253" s="1"/>
-      <c r="E253" s="1"/>
+      <c r="A253" s="7" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A254" s="8" t="s">
-        <v>239</v>
-      </c>
+      <c r="A254" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B254" s="1">
+        <v>21.430389255894248</v>
+      </c>
+      <c r="C254" s="1">
+        <v>26.965475521148146</v>
+      </c>
+      <c r="D254" s="1">
+        <v>51.604135222957602</v>
+      </c>
+      <c r="E254" s="7">
+        <v>22.924999999999997</v>
+      </c>
+      <c r="F254" s="1"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A255" s="2" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B255" s="1">
-        <v>21.430389255894248</v>
+        <v>22.128204893880628</v>
       </c>
       <c r="C255" s="1">
-        <v>26.965475521148146</v>
+        <v>25.955520422501806</v>
       </c>
       <c r="D255" s="1">
-        <v>51.604135222957602</v>
-      </c>
-      <c r="E255" s="1">
-        <v>22.924999999999997</v>
-      </c>
-      <c r="F255" s="1"/>
+        <v>51.916274683617573</v>
+      </c>
+      <c r="E255" s="7">
+        <v>21.439</v>
+      </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A256" s="2" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B256" s="1">
-        <v>22.128204893880628</v>
+        <v>20.829337560990467</v>
       </c>
       <c r="C256" s="1">
-        <v>25.955520422501806</v>
+        <v>29.114613297757032</v>
       </c>
       <c r="D256" s="1">
-        <v>51.916274683617573</v>
-      </c>
-      <c r="E256" s="1">
-        <v>21.439</v>
+        <v>50.056049141252501</v>
+      </c>
+      <c r="E256" s="7">
+        <v>16.077999999999996</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A257" s="2" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B257" s="1">
-        <v>20.829337560990467</v>
+        <v>21.705822290085518</v>
       </c>
       <c r="C257" s="1">
-        <v>29.114613297757032</v>
+        <v>27.017528783250778</v>
       </c>
       <c r="D257" s="1">
-        <v>50.056049141252501</v>
-      </c>
-      <c r="E257" s="1">
-        <v>16.077999999999996</v>
+        <v>51.276648926663711</v>
+      </c>
+      <c r="E257" s="7">
+        <v>24.505000000000003</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A258" s="2" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B258" s="1">
-        <v>21.705822290085518</v>
+        <v>21.791298461968765</v>
       </c>
       <c r="C258" s="1">
-        <v>27.017528783250778</v>
+        <v>27.364802929869448</v>
       </c>
       <c r="D258" s="1">
-        <v>51.276648926663711</v>
-      </c>
-      <c r="E258" s="1">
-        <v>24.505000000000003</v>
+        <v>50.843898608161794</v>
+      </c>
+      <c r="E258" s="7">
+        <v>19.292000000000002</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A259" s="2" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B259" s="1">
-        <v>21.791298461968765</v>
+        <v>21.192319613732408</v>
       </c>
       <c r="C259" s="1">
-        <v>27.364802929869448</v>
+        <v>28.338815789473685</v>
       </c>
       <c r="D259" s="1">
-        <v>50.843898608161794</v>
-      </c>
-      <c r="E259" s="1">
-        <v>19.292000000000002</v>
+        <v>50.468864596793914</v>
+      </c>
+      <c r="E259" s="7">
+        <v>17.128</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A260" s="2" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B260" s="1">
-        <v>21.192319613732408</v>
+        <v>21.588540271052686</v>
       </c>
       <c r="C260" s="1">
-        <v>28.338815789473685</v>
+        <v>27.37495714149744</v>
       </c>
       <c r="D260" s="1">
-        <v>50.468864596793914</v>
-      </c>
-      <c r="E260" s="1">
-        <v>17.128</v>
+        <v>51.036502587449874</v>
+      </c>
+      <c r="E260" s="7">
+        <v>15.622999999999999</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A261" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B261" s="1">
-        <v>21.588540271052686</v>
+        <v>21.863623358319593</v>
       </c>
       <c r="C261" s="1">
-        <v>27.37495714149744</v>
+        <v>26.850198981346523</v>
       </c>
       <c r="D261" s="1">
-        <v>51.036502587449874</v>
-      </c>
-      <c r="E261" s="1">
-        <v>15.622999999999999</v>
+        <v>51.286177660333877</v>
+      </c>
+      <c r="E261" s="7">
+        <v>22.509</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A262" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B262" s="1">
+        <v>21.705014313514216</v>
+      </c>
+      <c r="C262" s="1">
+        <v>27.560433735345626</v>
+      </c>
+      <c r="D262" s="1">
+        <v>50.734551951140155</v>
+      </c>
+      <c r="E262" s="7">
+        <v>9.0990000000000002</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A264" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B265" s="1">
+        <v>19.795421443498149</v>
+      </c>
+      <c r="C265" s="1">
+        <v>31.721322145003764</v>
+      </c>
+      <c r="D265" s="1">
+        <v>48.48325641149809</v>
+      </c>
+      <c r="E265" s="7">
+        <v>10.928999999999998</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B266" s="1">
+        <v>20.490013943039727</v>
+      </c>
+      <c r="C266" s="1">
+        <v>31.925572457418411</v>
+      </c>
+      <c r="D266" s="1">
+        <v>47.584413599541868</v>
+      </c>
+      <c r="E266" s="7">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B267" s="1">
+        <v>22.262760202424111</v>
+      </c>
+      <c r="C267" s="1">
+        <v>27.839512139143139</v>
+      </c>
+      <c r="D267" s="1">
+        <v>49.897727658432743</v>
+      </c>
+      <c r="E267" s="7">
+        <v>17.590000000000003</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B268" s="1">
+        <v>20.305574944203535</v>
+      </c>
+      <c r="C268" s="1">
+        <v>29.760265234711792</v>
+      </c>
+      <c r="D268" s="1">
+        <v>49.934159821084677</v>
+      </c>
+      <c r="E268" s="7">
+        <v>17.921999999999997</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B269" s="1">
+        <v>21.394517472603077</v>
+      </c>
+      <c r="C269" s="1">
+        <v>28.644775728804341</v>
+      </c>
+      <c r="D269" s="1">
+        <v>49.960706798592582</v>
+      </c>
+      <c r="E269" s="7">
+        <v>18.056000000000001</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B270" s="1">
+        <v>21.549088521073195</v>
+      </c>
+      <c r="C270" s="1">
+        <v>26.499062013489684</v>
+      </c>
+      <c r="D270" s="1">
+        <v>51.951849465437121</v>
+      </c>
+      <c r="E270" s="7">
+        <v>21.844000000000001</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B271" s="1">
+        <v>19.567245152330823</v>
+      </c>
+      <c r="C271" s="1">
+        <v>32.568331145503073</v>
+      </c>
+      <c r="D271" s="1">
+        <v>47.864423702166107</v>
+      </c>
+      <c r="E271" s="7">
+        <v>15.667999999999999</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B272" s="1">
+        <v>20.909851523622539</v>
+      </c>
+      <c r="C272" s="1">
+        <v>28.741652055230517</v>
+      </c>
+      <c r="D272" s="1">
+        <v>50.34849642114694</v>
+      </c>
+      <c r="E272" s="7">
+        <v>17.632999999999999</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B262" s="1">
-        <v>21.863623358319593</v>
-      </c>
-      <c r="C262" s="1">
-        <v>26.850198981346523</v>
-      </c>
-      <c r="D262" s="1">
-        <v>51.286177660333877</v>
-      </c>
-      <c r="E262" s="1">
-        <v>22.509</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A263" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B263" s="1">
-        <v>21.705014313514216</v>
-      </c>
-      <c r="C263" s="1">
-        <v>27.560433735345626</v>
-      </c>
-      <c r="D263" s="1">
-        <v>50.734551951140155</v>
-      </c>
-      <c r="E263" s="1">
-        <v>9.0990000000000002</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="B264" s="1"/>
-      <c r="C264" s="1"/>
-      <c r="D264" s="1"/>
-      <c r="E264" s="1"/>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A265" s="8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B266" s="1">
-        <v>19.795421443498149</v>
-      </c>
-      <c r="C266" s="1">
-        <v>31.721322145003764</v>
-      </c>
-      <c r="D266" s="1">
-        <v>48.48325641149809</v>
-      </c>
-      <c r="E266" s="1">
-        <v>10.928999999999998</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="B267" s="1">
-        <v>20.490013943039727</v>
-      </c>
-      <c r="C267" s="1">
-        <v>31.925572457418411</v>
-      </c>
-      <c r="D267" s="1">
-        <v>47.584413599541868</v>
-      </c>
-      <c r="E267" s="1">
-        <v>8.32</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A268" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="B268" s="1">
-        <v>22.262760202424111</v>
-      </c>
-      <c r="C268" s="1">
-        <v>27.839512139143139</v>
-      </c>
-      <c r="D268" s="1">
-        <v>49.897727658432743</v>
-      </c>
-      <c r="E268" s="1">
-        <v>17.590000000000003</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A269" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B269" s="1">
-        <v>20.305574944203535</v>
-      </c>
-      <c r="C269" s="1">
-        <v>29.760265234711792</v>
-      </c>
-      <c r="D269" s="1">
-        <v>49.934159821084677</v>
-      </c>
-      <c r="E269" s="1">
-        <v>17.921999999999997</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A270" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B270" s="1">
-        <v>21.394517472603077</v>
-      </c>
-      <c r="C270" s="1">
-        <v>28.644775728804341</v>
-      </c>
-      <c r="D270" s="1">
-        <v>49.960706798592582</v>
-      </c>
-      <c r="E270" s="1">
-        <v>18.056000000000001</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A271" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B271" s="1">
-        <v>21.549088521073195</v>
-      </c>
-      <c r="C271" s="1">
-        <v>26.499062013489684</v>
-      </c>
-      <c r="D271" s="1">
-        <v>51.951849465437121</v>
-      </c>
-      <c r="E271" s="1">
-        <v>21.844000000000001</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A272" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="B272" s="1">
-        <v>19.567245152330823</v>
-      </c>
-      <c r="C272" s="1">
-        <v>32.568331145503073</v>
-      </c>
-      <c r="D272" s="1">
-        <v>47.864423702166107</v>
-      </c>
-      <c r="E272" s="1">
-        <v>15.667999999999999</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A273" s="6" t="s">
-        <v>257</v>
-      </c>
       <c r="B273" s="1">
-        <v>20.909851523622539</v>
+        <v>21.156427188072868</v>
       </c>
       <c r="C273" s="1">
-        <v>28.741652055230517</v>
+        <v>30.310398865387313</v>
       </c>
       <c r="D273" s="1">
-        <v>50.34849642114694</v>
-      </c>
-      <c r="E273" s="1">
-        <v>17.632999999999999</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A274" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="B274" s="1">
-        <v>21.156427188072868</v>
-      </c>
-      <c r="C274" s="1">
-        <v>30.310398865387313</v>
-      </c>
-      <c r="D274" s="1">
         <v>48.533173946539833</v>
       </c>
-      <c r="E274" s="1">
+      <c r="E273" s="7">
         <v>9.3419999999999987</v>
       </c>
     </row>
